--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y177"/>
+  <dimension ref="A1:Y186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "" vs "000" :: should be in print in that city before it _â€¢ 000 ...</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "" vs "000" :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: THIS OFFICE:ä¸€</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: THIS OFFICE:一</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ï»¿â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: isolated marker/symbol line :: n</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: E</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -650,7 +654,7 @@
       </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L506: line starts with punctuation glued to text :: .centre of the Moons shadow in this</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • en</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>729</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -708,24 +712,24 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00B8 CEDILLA | isolated marker/symbol line :: å�¸</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+53F8 CJK UNIFIED IDEOGRAPH-53F8 | isolated marker/symbol line :: 司</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ en</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • en</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00B8 CEDILLA | isolated marker/symbol line :: å�¸</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+53F8 CJK UNIFIED IDEOGRAPH-53F8 | isolated marker/symbol line :: 司</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L221: symbol-only separator/garbage line :: 000-</t>
+          <t>L139: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -741,7 +745,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L856: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aCoavia (odd internal casing) :: aCoavia him</t>
+          <t>L506: line starts with punctuation glued to text :: .centre of the Moons shadow in this</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -786,17 +790,17 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.â€”The NewIPee like Lady Palmerstonâ€™s</t>
+          <t>L745: suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.—The NewIPee like Lady Palmerston’s</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: known that there is a large tractâ€”al-</t>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+5DF2 CJK UNIFIED IDEOGRAPH-5DF2 | isolated marker/symbol line :: 已</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: was informed it had been left byâ€¢</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: was informed it had been left by•</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -808,7 +812,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L225: symbol-only separator/garbage line :: 528,00</t>
+          <t>L221: symbol-only separator/garbage line :: 000-</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -824,7 +828,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
+          <t>L856: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aCoavia (odd internal casing) :: aCoavia him</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -846,12 +850,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -874,24 +878,24 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Crops.- The Midge. â€” This</t>
+          <t>L88: stray/suspicious non-ASCII glyph(s): U+66F2 CJK UNIFIED IDEOGRAPH-66F2 | isolated marker/symbol line :: 曲</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of age and an American by birth.â€”</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Tavern Licences,... •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: X</t>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+5DF2 CJK UNIFIED IDEOGRAPH-5DF2 | isolated marker/symbol line :: 已</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L227: symbol-only separator/garbage line :: 3,50</t>
+          <t>L225: symbol-only separator/garbage line :: 528,00</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -907,7 +911,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L988: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 2Deals (letter/digit mix), LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: 2Deals to D.G. LaBarre Esq.... 2,56</t>
+          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -957,24 +961,24 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L256: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: form.â€”The annual meeting of the Abo-</t>
+          <t>L247: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: - 000-</t>
+          <t>L78: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L229: symbol-only separator/garbage line :: 60,00</t>
+          <t>L227: symbol-only separator/garbage line :: 3,50</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -988,7 +992,11 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L988: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 2Deals (letter/digit mix), LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: 2Deals to D.G. LaBarre Esq.... 2,56</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1036,24 +1044,24 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦</t>
+          <t>L265: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dians of Canada and Hudsonâ€™s Bay</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "" vs "000" :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L97: symbol-only separator/garbage line :: - 000</t>
+          <t>L88: stray/suspicious non-ASCII glyph(s): U+66F2 CJK UNIFIED IDEOGRAPH-66F2 | isolated marker/symbol line :: 曲</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L231: symbol-only separator/garbage line :: 892,00</t>
+          <t>L229: symbol-only separator/garbage line :: 60,00</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1111,24 +1119,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR :: Merchantâ€™s Liquor Licence,â€¦., .</t>
+          <t>L304: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” BOOK AND JOB PRINTING</t>
+          <t>L874: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: to turn the wilderness into • fruitful cess which he has acheived in establish I transferred to the Hondurean Govern</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 10</t>
+          <t>L92: symbol-only separator/garbage line :: - 000-</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L231: symbol-only separator/garbage line :: 892,00</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 'Merchantâ€™s Liquor Licence,.... 512,0</t>
+          <t>L112: punctuation artifact: repeated periods :: 'Merchant’s Liquor Licence,.... 512,0</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1186,24 +1194,24 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L265: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L467: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 'Merchantâ€™s Liquor Licence,.... 512,0</t>
+          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Maurice Sayer damage €</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L178: isolated marker/symbol line :: y</t>
+          <t>L97: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L336: isolated marker/symbol line :: 15</t>
+          <t>L247: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1233,12 +1241,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1261,24 +1269,24 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L328: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: so numerous aod so well authenticated. Paid to Ludger Dupont â€¦</t>
+          <t>L573: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F | isolated marker/symbol line :: 小</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Pedlarâ€™s Licence, ...................13,00</t>
+          <t>L1009: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: are not it is true very rich, but they Party.•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L201: isolated marker/symbol line :: S</t>
+          <t>L148: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L339: symbol-only separator/garbage line :: $6375,09</t>
+          <t>L336: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1313,7 +1321,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1331,29 +1339,25 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
+          <t>L878: punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: —._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: perhaps $4.800 each â€” we suppose paid</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Tavern Licences,... â€¢</t>
-        </is>
-      </c>
+          <t>L622: stray/suspicious non-ASCII glyph(s): U+6FB3 CJK UNIFIED IDEOGRAPH-6FB3, U+4E30 CJK UNIFIED IDEOGRAPH-4E30, U+8D39 CJK UNIFIED IDEOGRAPH-8D39, U+5BB9 CJK UNIFIED IDEOGRAPH-5BB9 :: 澳 丰 费 容</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L206: isolated marker/symbol line :: -</t>
+          <t>L178: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L358: isolated marker/symbol line :: 70</t>
+          <t>L339: symbol-only separator/garbage line :: $6375,09</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Pedlarâ€™s Licence, ...................13,00</t>
+          <t>L118: punctuation artifact: repeated periods :: Pedlar’s Licence, ...................13,00</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1383,12 +1387,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1407,24 +1411,20 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Solar 000-Eclipse.â€” The path of ihe</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: property â€˜</t>
-        </is>
-      </c>
+          <t>L680: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L201: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L372: isolated marker/symbol line :: 10</t>
+          <t>L358: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1469,29 +1469,25 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,â€” effect upon the base and slanderousingthe freedom of the Bay Islanders she wasnâ€™t Â°uch a big ship after all would commence on...</t>
+          <t>L895: suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,— effect upon the base and slanderousingthe freedom of the Bay Islanders she wasn’t °uch a big ship after all would commence on the2...</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: known that there is a large tractâ€”al-</t>
-        </is>
-      </c>
+          <t>L686: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L218: symbol-only separator/garbage line :: 422.46</t>
+          <t>L206: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: 75.00</t>
+          <t>L372: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1522,7 +1518,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1532,35 +1528,31 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
+          <t>L904: punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : — The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L469: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Steamship United States ground except under the regulationsâ€”that the</t>
-        </is>
-      </c>
+          <t>L714: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L219: isolated marker/symbol line :: "</t>
+          <t>L216: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L387: symbol-only separator/garbage line :: 18.69</t>
+          <t>L385: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Tavern Licences,... â€¢</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Tavern Licences,... •</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1600,24 +1592,20 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L549: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hollowayâ€™s Pills.â€”There is no ha-</t>
-        </is>
-      </c>
+          <t>L716: stray/suspicious non-ASCII glyph(s): U+603B CJK UNIFIED IDEOGRAPH-603B | isolated marker/symbol line :: 总</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L221: symbol-only separator/garbage line :: ****</t>
+          <t>L217: isolated marker/symbol line :: ……</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L389: symbol-only separator/garbage line :: 2.00</t>
+          <t>L387: symbol-only separator/garbage line :: 18.69</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1659,24 +1647,20 @@
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal â€” A report in current in</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Professor Hollowayâ€™s remediesin this</t>
-        </is>
-      </c>
+          <t>L786: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L222: symbol-only separator/garbage line :: 14207</t>
+          <t>L218: symbol-only separator/garbage line :: 422.46</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L456: symbol-only separator/garbage line :: 10.00</t>
+          <t>L389: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1718,30 +1702,26 @@
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å°�</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L881: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: - 000 一</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L224: isolated marker/symbol line :: **</t>
+          <t>L219: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L458: isolated marker/symbol line :: 800</t>
+          <t>L456: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rue. Esquireâ€™s barn, .....</t>
+          <t>L353: punctuation artifact: repeated periods :: rue. Esquire’s barn, .....</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1765,24 +1745,20 @@
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Liverpool, Jope 23.â€” Breadstuffs.</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to AimÃ©</t>
-        </is>
-      </c>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L225: symbol-only separator/garbage line :: 3.10</t>
+          <t>L221: symbol-only separator/garbage line :: ****</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L460: symbol-only separator/garbage line :: 4.00</t>
+          <t>L458: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1812,24 +1788,20 @@
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L622: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00B4 ACUTE ACCENT, U+00AE REGISTERED SIGN :: æ¾³ ä¸° è´¹ å®¹</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Crops.â€” The Midge. â€” This</t>
-        </is>
-      </c>
+          <t>L958: stray/suspicious non-ASCII glyph(s): U+65B0 CJK UNIFIED IDEOGRAPH-65B0 | isolated marker/symbol line :: 新</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L227: isolated marker/symbol line :: .</t>
+          <t>L222: symbol-only separator/garbage line :: 14207</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L462: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L460: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1859,24 +1831,20 @@
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L634: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: To John Prouart. apprÃ©ciÃ©</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L263: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: morning, says the St. Catherineâ€™s Jour-</t>
-        </is>
-      </c>
+          <t>L1036: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L228: symbol-only separator/garbage line :: 38.00</t>
+          <t>L224: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L464: symbol-only separator/garbage line :: 8.00</t>
+          <t>L462: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1906,24 +1874,20 @@
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L686: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rue. Esquireâ€™s barn, .....</t>
-        </is>
-      </c>
+          <t>L1048: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L230: symbol-only separator/garbage line :: 5.25</t>
+          <t>L225: symbol-only separator/garbage line :: 3.10</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L466: symbol-only separator/garbage line :: 5.00</t>
+          <t>L464: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1953,24 +1917,20 @@
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L716: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: æ€»</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: tion No. Aâ€”.............</t>
-        </is>
-      </c>
+          <t>L1051: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L231: symbol-only separator/garbage line :: 6.25</t>
+          <t>L227: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L468: symbol-only separator/garbage line :: 8.00</t>
+          <t>L466: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -2000,30 +1960,26 @@
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about which there is no doubt â€” to</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tie Grave of Eve.â€”In the old grave-</t>
-        </is>
-      </c>
+          <t>L1063: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L233: symbol-only separator/garbage line :: 5120</t>
+          <t>L228: symbol-only separator/garbage line :: 38.00</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 0</t>
+          <t>L468: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: tion No. Aâ€”.............</t>
+          <t>L412: punctuation artifact: repeated periods :: tion No. A—.............</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2045,26 +2001,18 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: world â€” a system of which any country</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: moss-covered tombstone containing theâ€˜</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L235: isolated marker/symbol line :: .</t>
+          <t>L230: symbol-only separator/garbage line :: 5.25</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L520: symbol-only separator/garbage line :: 4 00</t>
+          <t>L470: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2092,26 +2040,18 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: following inscription :â€”</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L236: symbol-only separator/garbage line :: 59, 66</t>
+          <t>L231: symbol-only separator/garbage line :: 6.25</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L521: isolated marker/symbol line :: 18</t>
+          <t>L520: symbol-only separator/garbage line :: 4 00</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2139,26 +2079,18 @@
       <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” London Corres. N. O. Delta.</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 28th, 1735, in ye 78th year of her age.â€�</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L238: symbol-only separator/garbage line :: 383.25</t>
+          <t>L233: symbol-only separator/garbage line :: 5120</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L523: symbol-only separator/garbage line :: 100.00</t>
+          <t>L521: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2186,26 +2118,18 @@
       <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L879: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: tÃ¤gger, the American Niagara was</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L240: symbol-only separator/garbage line :: 1100</t>
+          <t>L235: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L539: symbol-only separator/garbage line :: 24.00</t>
+          <t>L523: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2233,26 +2157,18 @@
       <c r="G28" s="1" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: - 000 ä¸€</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "" vs "000" :: should be in print in that city before it _â€¢ 000 ...</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L242: isolated marker/symbol line :: 700</t>
+          <t>L236: symbol-only separator/garbage line :: 59, 66</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L544: isolated marker/symbol line :: G.</t>
+          <t>L539: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2280,26 +2196,18 @@
       <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L896: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ashes quietâ€”Pots 27s 6d to 29 3d;</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: can be received at Quebec or Montreal, The Solar Eclipse.â€”Thepath of the</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L244: symbol-only separator/garbage line :: 42.97</t>
+          <t>L238: symbol-only separator/garbage line :: 383.25</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: 50</t>
+          <t>L544: isolated marker/symbol line :: G.</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2327,26 +2235,18 @@
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis â€” -</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L246: symbol-only separator/garbage line :: 528, 00</t>
+          <t>L240: symbol-only separator/garbage line :: 1100</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L562: symbol-only separator/garbage line :: 4.05</t>
+          <t>L560: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2374,32 +2274,24 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L1035: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Joseph Giroux.â€¦.</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L555: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œtotal darkness" at the above place</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L248: symbol-only separator/garbage line :: 3.50</t>
+          <t>L242: isolated marker/symbol line :: 700</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: J.</t>
+          <t>L562: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "" vs "000" :: should be in print in that city before it _â€¢ 000 ...</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | localized OCR phrase divergence vs other OCR: "" vs "000" :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2421,32 +2313,24 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L1048: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Moonâ€™s shadow, 100 miles or 50 to</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L250: symbol-only separator/garbage line :: 60, 00</t>
+          <t>L244: symbol-only separator/garbage line :: 42.97</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L576: symbol-only separator/garbage line :: 4 50</t>
+          <t>L566: isolated marker/symbol line :: J.</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis â€” -</t>
+          <t>L514: punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis — -</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2468,26 +2352,18 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal.â€”A report is current in</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L253: symbol-only separator/garbage line :: 892, 00</t>
+          <t>L246: symbol-only separator/garbage line :: 528, 00</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: 37</t>
+          <t>L576: symbol-only separator/garbage line :: 4 50</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2516,21 +2392,17 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Englandâ€™s Premier.-Lord Palmerston</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L255: isolated marker/symbol line :: S</t>
+          <t>L248: symbol-only separator/garbage line :: 3.50</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: 90</t>
+          <t>L578: isolated marker/symbol line :: 37</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2559,21 +2431,17 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: perhaps $4,800 eachâ€”we suppose paid</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L258: symbol-only separator/garbage line :: 1906.30</t>
+          <t>L250: symbol-only separator/garbage line :: 60, 00</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 1.00</t>
+          <t>L580: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2602,21 +2470,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: quarterly, â€”the one for doing little or</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L260: isolated marker/symbol line :: 30</t>
+          <t>L253: symbol-only separator/garbage line :: 892, 00</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L584: isolated marker/symbol line :: 70</t>
+          <t>L582: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2645,21 +2509,17 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L682: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: What effect the mining excitement down Toronto University.â€”Ed. Wit."</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L264: isolated marker/symbol line :: 70</t>
+          <t>L255: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L625: symbol-only separator/garbage line :: 1.25</t>
+          <t>L584: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2688,21 +2548,17 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing down smack on his headâ€”"Pam" Regiments for operations on land. All</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L265: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L256: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 7.25</t>
+          <t>L625: symbol-only separator/garbage line :: 1.25</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2731,27 +2587,23 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L737: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L270: symbol-only separator/garbage line :: 75.00</t>
+          <t>L258: symbol-only separator/garbage line :: 1906.30</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: **</t>
+          <t>L627: symbol-only separator/garbage line :: 7.25</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe â€”000--------</t>
+          <t>L758: punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe —000--------</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2774,27 +2626,23 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.â€”The NewIPee like Lady Palmerstonâ€™s</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L273: symbol-only separator/garbage line :: 18.69</t>
+          <t>L260: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L630: symbol-only separator/garbage line :: 2.00</t>
+          <t>L628: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: strongâ€™s fire, .............</t>
+          <t>L764: punctuation artifact: repeated periods :: strong’s fire, .............</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2817,21 +2665,17 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Clem y eyed man of destiny,â€�leftdresses ? Because they are muzzling</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L275: symbol-only separator/garbage line :: 1.00</t>
+          <t>L264: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L632: isolated marker/symbol line :: P</t>
+          <t>L630: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2860,21 +2704,17 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe â€”000--------</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L282: symbol-only separator/garbage line :: 10.00</t>
+          <t>L265: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L641: isolated marker/symbol line :: 000</t>
+          <t>L632: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2903,21 +2743,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: strongâ€™s fire, .............</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L285: isolated marker/symbol line :: 800</t>
+          <t>L270: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L688: symbol-only separator/garbage line :: 16 00</t>
+          <t>L641: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2946,21 +2782,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Liverpool, June *3. â€” Breadstuffâ€™s</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L287: isolated marker/symbol line :: 400</t>
+          <t>L273: symbol-only separator/garbage line :: 18.69</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L690: symbol-only separator/garbage line :: 1.35</t>
+          <t>L688: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2989,21 +2821,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ashes quietâ€”Pots 27s 6d to 29 3d ;</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L288: isolated marker/symbol line :: 100</t>
+          <t>L275: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L694: isolated marker/symbol line :: F</t>
+          <t>L690: symbol-only separator/garbage line :: 1.35</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3032,21 +2860,17 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London.â€”Money higher and active</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L291: isolated marker/symbol line :: .</t>
+          <t>L282: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L695: isolated marker/symbol line :: J</t>
+          <t>L694: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3075,27 +2899,23 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: to turn the wilderness into â€¢ fruitful cess which he has acheived in establish I transferred to the Hondurean Govern</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L292: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L285: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L697: isolated marker/symbol line :: a</t>
+          <t>L695: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, â€žâ€”.._._11_T_._.</t>
+          <t>L876: punctuation artifact: repeated periods :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, „—.._._11_T_._.</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3118,27 +2938,23 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, â€žâ€”.._._11_T_._.</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 2</t>
+          <t>L287: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L729: symbol-only separator/garbage line :: 1.00</t>
+          <t>L697: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
+          <t>L878: punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: —._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
         </is>
       </c>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3161,21 +2977,17 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L320: symbol-only separator/garbage line :: 81.</t>
+          <t>L288: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L731: symbol-only separator/garbage line :: 2.00</t>
+          <t>L729: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3204,27 +3016,23 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the attention of the public as to lead to worldâ€”a system of which any country tuated as much by an ultimate design of sp stators, the rigging of the ship- the harbou...</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L325: symbol-only separator/garbage line :: 6375, 00</t>
+          <t>L291: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L733: symbol-only separator/garbage line :: 5.00</t>
+          <t>L731: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
+          <t>L904: punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : — The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3247,21 +3055,17 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the neglect of those resources upon might well be proudâ€”has laid Canada Iragua as to punish Guardiola, the pre pingin the vicinity was filled with ad- Revenue the pa...</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L330: isolated marker/symbol line :: 1</t>
+          <t>L292: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L735: symbol-only separator/garbage line :: 334.31</t>
+          <t>L733: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3290,21 +3094,17 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L889: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of no country rests on a sound founda- of his country's chief benefactors. Dr.is an unmitigated despotism, and the an irrevocable stupidity. They leanerdarmy after hav...</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L331: isolated marker/symbol line :: 0</t>
+          <t>L304: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L834: symbol-only separator/garbage line :: 0.25</t>
+          <t>L735: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3333,21 +3133,17 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,â€” effect upon the base and slanderousingthe freedom of the Bay Islanders she wasnâ€™t Â°uch a big ship after all would commence on...</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L400: isolated marker/symbol line :: 2</t>
+          <t>L318: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L835: isolated marker/symbol line :: $</t>
+          <t>L834: symbol-only separator/garbage line :: 0.25</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3376,27 +3172,23 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ^=^ he see an extensive Blackwoodâ€™s Magazine-The Juwecommand. â€” Robbing a Tracer -On Saterday of Baltimore." The Aperigan Minister</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L436: isolated marker/symbol line :: 000</t>
+          <t>L320: symbol-only separator/garbage line :: 81.</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L845: isolated marker/symbol line :: E-</t>
+          <t>L835: isolated marker/symbol line :: $</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........â€” 4,511</t>
+          <t>L918: punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........— 4,511</t>
         </is>
       </c>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3419,21 +3211,17 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L325: symbol-only separator/garbage line :: 6375, 00</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L864: isolated marker/symbol line :: .:</t>
+          <t>L845: isolated marker/symbol line :: E-</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3462,21 +3250,17 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........â€” 4,511</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L468: isolated marker/symbol line :: 000</t>
+          <t>L330: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L865: symbol-only separator/garbage line :: 5,31</t>
+          <t>L864: isolated marker/symbol line :: .:</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3505,21 +3289,17 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Maurice Sayer damage â‚¬</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L476: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "000" vs "last thing in town attributed to Lord" :: 000</t>
+          <t>L331: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: -</t>
+          <t>L865: symbol-only separator/garbage line :: 5,31</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3548,21 +3328,17 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L983: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: For M. Aaron Hart (RiviÃ¨re du</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L486: isolated marker/symbol line :: 1</t>
+          <t>L400: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L867: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...10,80</t>
+          <t>L866: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3591,21 +3367,17 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: - Joseph Duval.â€” ................1,60:</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å°�</t>
+          <t>L436: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L869: symbol-only separator/garbage line :: 5,00</t>
+          <t>L867: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...10,80</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3634,21 +3406,17 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L995: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoine DÃ©lorier 4 do. 24,00</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L595: symbol-only separator/garbage line :: 8.00</t>
+          <t>L467: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L870: symbol-only separator/garbage line :: .... 750</t>
+          <t>L869: symbol-only separator/garbage line :: 5,00</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3677,21 +3445,17 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1005: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The extent end richness of the mine of clair.â€”Part V. Scottish National Cha"</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L598: isolated marker/symbol line :: *</t>
+          <t>L468: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L871: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 20,00</t>
+          <t>L870: symbol-only separator/garbage line :: .... 750</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3720,21 +3484,17 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1009: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: are not it is true very rich, but they Party.â€¢</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L599: symbol-only separator/garbage line :: 5.00</t>
+          <t>L476: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "000" vs "last thing in town attributed to Lord" :: 000</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
+          <t>L871: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 20,00</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3763,21 +3523,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: quote/punctuation debris :: from Peterboroâ€™, and mysteriously dis-steamerleft.,â€”., .â€ž</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: 400</t>
+          <t>L486: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L929: symbol-only separator/garbage line :: $116,374</t>
+          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3806,21 +3562,17 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1026: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: -â€˜</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L610: symbol-only separator/garbage line :: 100.00</t>
+          <t>L573: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F | isolated marker/symbol line :: 小</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L947: symbol-only separator/garbage line :: 1,00</t>
+          <t>L929: symbol-only separator/garbage line :: $116,374</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3854,12 +3606,12 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L614: isolated marker/symbol line :: **</t>
+          <t>L595: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L949: isolated marker/symbol line :: 1</t>
+          <t>L947: symbol-only separator/garbage line :: 1,00</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3893,12 +3645,12 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: *</t>
+          <t>L598: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L951: symbol-only separator/garbage line :: 5,1</t>
+          <t>L949: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -3932,18 +3684,18 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L616: symbol-only separator/garbage line :: 94.00</t>
+          <t>L599: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L960: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 20,00</t>
+          <t>L951: symbol-only separator/garbage line :: 5,1</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr">
         <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: - Joseph Duval.â€” ................1,60:</t>
+          <t>L990: punctuation artifact: repeated periods :: - Joseph Duval.— ................1,60:</t>
         </is>
       </c>
       <c r="R67" s="1" t="inlineStr"/>
@@ -3971,12 +3723,12 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L619: isolated marker/symbol line :: "</t>
+          <t>L606: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L961: isolated marker/symbol line :: - #</t>
+          <t>L960: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 20,00</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4010,12 +3762,12 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L623: isolated marker/symbol line :: 0</t>
+          <t>L610: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L969: symbol-only separator/garbage line :: 220,00</t>
+          <t>L961: isolated marker/symbol line :: - #</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4049,20 +3801,16 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L626: isolated marker/symbol line :: 06</t>
+          <t>L614: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L970: symbol-only separator/garbage line :: 6,00</t>
+          <t>L969: symbol-only separator/garbage line :: 220,00</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: quote/punctuation debris :: from Peterboroâ€™, and mysteriously dis-steamerleft.,â€”., .â€ž</t>
-        </is>
-      </c>
+      <c r="Q70" s="1" t="inlineStr"/>
       <c r="R70" s="1" t="inlineStr"/>
       <c r="S70" s="1" t="inlineStr"/>
       <c r="T70" s="1" t="inlineStr"/>
@@ -4088,12 +3836,12 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L636: isolated marker/symbol line :: a</t>
+          <t>L615: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L999: isolated marker/symbol line :: 0</t>
+          <t>L970: symbol-only separator/garbage line :: 6,00</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4123,12 +3871,12 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L637: isolated marker/symbol line :: 1</t>
+          <t>L616: symbol-only separator/garbage line :: 94.00</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L1001: symbol-only separator/garbage line :: 9,16</t>
+          <t>L999: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4158,12 +3906,12 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L638: symbol-only separator/garbage line :: 1.00</t>
+          <t>L619: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L1022: isolated marker/symbol line :: %</t>
+          <t>L1001: symbol-only separator/garbage line :: 9,16</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4193,12 +3941,12 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L646: isolated marker/symbol line :: 8</t>
+          <t>L623: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L1024: isolated marker/symbol line :: -</t>
+          <t>L1022: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4228,12 +3976,12 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L648: isolated marker/symbol line :: 3</t>
+          <t>L626: isolated marker/symbol line :: 06</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L1028: isolated marker/symbol line :: a</t>
+          <t>L1024: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4263,12 +4011,12 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L649: isolated marker/symbol line :: 2</t>
+          <t>L636: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: ,</t>
+          <t>L1026: isolated marker/symbol line :: -‘</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4298,12 +4046,12 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L654: isolated marker/symbol line :: 7</t>
+          <t>L637: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L1032: isolated marker/symbol line :: -1</t>
+          <t>L1028: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4333,12 +4081,12 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L655: isolated marker/symbol line :: 1</t>
+          <t>L638: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: %</t>
+          <t>L1030: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4368,12 +4116,12 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L657: symbol-only separator/garbage line :: 2.00</t>
+          <t>L646: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L1036: isolated marker/symbol line :: 1</t>
+          <t>L1032: isolated marker/symbol line :: -1</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4403,12 +4151,12 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L662: symbol-only separator/garbage line :: 1600</t>
+          <t>L648: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L1038: isolated marker/symbol line :: %</t>
+          <t>L1034: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4438,12 +4186,12 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L667: isolated marker/symbol line :: 8</t>
+          <t>L649: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L1040: isolated marker/symbol line :: %</t>
+          <t>L1036: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4473,10 +4221,14 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L668: isolated marker/symbol line :: '</t>
-        </is>
-      </c>
-      <c r="O82" s="1" t="inlineStr"/>
+          <t>L654: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr">
+        <is>
+          <t>L1038: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="inlineStr"/>
       <c r="R82" s="1" t="inlineStr"/>
@@ -4504,10 +4256,14 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L671: isolated marker/symbol line :: d</t>
-        </is>
-      </c>
-      <c r="O83" s="1" t="inlineStr"/>
+          <t>L655: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O83" s="1" t="inlineStr">
+        <is>
+          <t>L1040: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr"/>
       <c r="R83" s="1" t="inlineStr"/>
@@ -4535,7 +4291,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L672: symbol-only separator/garbage line :: 1.00</t>
+          <t>L657: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4566,7 +4322,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L675: symbol-only separator/garbage line :: 2.00</t>
+          <t>L662: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4597,7 +4353,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L679: isolated marker/symbol line :: 0</t>
+          <t>L667: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4628,7 +4384,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L684: isolated marker/symbol line :: 4</t>
+          <t>L668: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4659,7 +4415,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L686: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
+          <t>L671: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4690,7 +4446,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: 2</t>
+          <t>L672: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4721,7 +4477,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L688: isolated marker/symbol line :: 6</t>
+          <t>L675: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4752,7 +4508,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L690: isolated marker/symbol line :: .</t>
+          <t>L679: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4783,7 +4539,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L698: isolated marker/symbol line :: *</t>
+          <t>L680: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4814,7 +4570,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L701: symbol-only separator/garbage line :: 33131</t>
+          <t>L684: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4845,7 +4601,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L705: isolated marker/symbol line :: 9</t>
+          <t>L686: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4876,7 +4632,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L706: isolated marker/symbol line :: 47</t>
+          <t>L687: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4907,7 +4663,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L709: isolated marker/symbol line :: G</t>
+          <t>L688: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -4938,7 +4694,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L710: isolated marker/symbol line :: 0</t>
+          <t>L690: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -4969,7 +4725,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: .</t>
+          <t>L698: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5000,7 +4756,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L713: isolated marker/symbol line :: 000</t>
+          <t>L701: symbol-only separator/garbage line :: 33131</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5031,7 +4787,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L715: isolated marker/symbol line :: 000</t>
+          <t>L705: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5062,7 +4818,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L716: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: æ€»</t>
+          <t>L706: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5093,7 +4849,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L717: isolated marker/symbol line :: D</t>
+          <t>L709: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5124,7 +4880,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L718: isolated marker/symbol line :: 3</t>
+          <t>L710: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5155,7 +4911,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L719: isolated marker/symbol line :: 2</t>
+          <t>L712: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5186,7 +4942,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L721: symbol-only separator/garbage line :: 9555</t>
+          <t>L713: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5217,7 +4973,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L722: isolated marker/symbol line :: 3</t>
+          <t>L714: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5248,7 +5004,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L728: isolated marker/symbol line :: c</t>
+          <t>L715: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5279,7 +5035,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L729: isolated marker/symbol line :: 4</t>
+          <t>L716: stray/suspicious non-ASCII glyph(s): U+603B CJK UNIFIED IDEOGRAPH-603B | isolated marker/symbol line :: 总</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5310,7 +5066,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
+          <t>L717: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5341,7 +5097,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L797: isolated marker/symbol line :: 4</t>
+          <t>L718: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5372,7 +5128,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L799: isolated marker/symbol line :: A</t>
+          <t>L719: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5403,7 +5159,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L833: isolated marker/symbol line :: &gt;</t>
+          <t>L721: symbol-only separator/garbage line :: 9555</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5434,7 +5190,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L855: isolated marker/symbol line :: 000</t>
+          <t>L722: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5465,7 +5221,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L882: isolated marker/symbol line :: 1</t>
+          <t>L728: isolated marker/symbol line :: c</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5496,7 +5252,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L898: isolated marker/symbol line :: '</t>
+          <t>L729: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5527,7 +5283,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L899: isolated marker/symbol line :: V</t>
+          <t>L786: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5558,7 +5314,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L912: isolated marker/symbol line :: A</t>
+          <t>L797: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5589,7 +5345,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L939: isolated marker/symbol line :: 4</t>
+          <t>L799: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5620,7 +5376,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L943: isolated marker/symbol line :: 0</t>
+          <t>L833: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5651,7 +5407,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L946: isolated marker/symbol line :: 1</t>
+          <t>L855: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5682,7 +5438,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L947: symbol-only separator/garbage line :: 3.00</t>
+          <t>L882: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5713,7 +5469,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L948: isolated marker/symbol line :: 2</t>
+          <t>L898: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5744,7 +5500,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L949: isolated marker/symbol line :: 3</t>
+          <t>L899: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5775,7 +5531,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L912: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5806,7 +5562,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L951: symbol-only separator/garbage line :: 3, 13</t>
+          <t>L939: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -5837,7 +5593,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L955: symbol-only separator/garbage line :: 10.80</t>
+          <t>L943: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -5868,7 +5624,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L957: isolated marker/symbol line :: 2</t>
+          <t>L946: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -5899,7 +5655,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L958: isolated marker/symbol line :: æ–°</t>
+          <t>L947: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -5930,7 +5686,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L960: symbol-only separator/garbage line :: 5.00</t>
+          <t>L948: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -5961,7 +5717,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L962: isolated marker/symbol line :: 780</t>
+          <t>L949: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -5992,7 +5748,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L963: isolated marker/symbol line :: D</t>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6023,7 +5779,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L965: symbol-only separator/garbage line :: 20.00</t>
+          <t>L951: symbol-only separator/garbage line :: 3, 13</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6054,7 +5810,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L968: symbol-only separator/garbage line :: 5.60</t>
+          <t>L955: symbol-only separator/garbage line :: 10.80</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6085,7 +5841,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L970: symbol-only separator/garbage line :: 2.50</t>
+          <t>L957: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6116,7 +5872,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L972: symbol-only separator/garbage line :: 2.00</t>
+          <t>L958: stray/suspicious non-ASCII glyph(s): U+65B0 CJK UNIFIED IDEOGRAPH-65B0 | isolated marker/symbol line :: 新</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6147,7 +5903,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L974: isolated marker/symbol line :: 8</t>
+          <t>L960: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6178,7 +5934,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L975: isolated marker/symbol line :: 03</t>
+          <t>L962: isolated marker/symbol line :: 780</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6209,7 +5965,7 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L976: isolated marker/symbol line :: 112</t>
+          <t>L963: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6240,7 +5996,7 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L979: isolated marker/symbol line :: 1</t>
+          <t>L965: symbol-only separator/garbage line :: 20.00</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6271,7 +6027,7 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L980: symbol-only separator/garbage line :: 11.2</t>
+          <t>L968: symbol-only separator/garbage line :: 5.60</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6302,7 +6058,7 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L982: symbol-only separator/garbage line :: 4516</t>
+          <t>L970: symbol-only separator/garbage line :: 2.50</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6333,7 +6089,7 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L984: isolated marker/symbol line :: 12</t>
+          <t>L972: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6364,7 +6120,7 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L986: isolated marker/symbol line :: D</t>
+          <t>L974: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6395,7 +6151,7 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L988: symbol-only separator/garbage line :: 7.10</t>
+          <t>L975: isolated marker/symbol line :: 03</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6426,7 +6182,7 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L991: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L976: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6457,7 +6213,7 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L993: symbol-only separator/garbage line :: 6, 60</t>
+          <t>L979: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6488,7 +6244,7 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L995: symbol-only separator/garbage line :: $11637</t>
+          <t>L980: symbol-only separator/garbage line :: 11.2</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6519,7 +6275,7 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L997: isolated marker/symbol line :: 4</t>
+          <t>L982: symbol-only separator/garbage line :: 4516</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6550,7 +6306,7 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L998: symbol-only separator/garbage line :: 1, 00</t>
+          <t>L984: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -6581,7 +6337,7 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L1002: isolated marker/symbol line :: -</t>
+          <t>L986: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -6612,7 +6368,7 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L1003: symbol-only separator/garbage line :: 5, 20</t>
+          <t>L988: symbol-only separator/garbage line :: 7.10</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -6643,7 +6399,7 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L1007: isolated marker/symbol line :: .</t>
+          <t>L991: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -6674,7 +6430,7 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L1008: symbol-only separator/garbage line :: 20, 00</t>
+          <t>L993: symbol-only separator/garbage line :: 6, 60</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -6705,7 +6461,7 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L1011: isolated marker/symbol line :: .</t>
+          <t>L995: symbol-only separator/garbage line :: $11637</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -6736,7 +6492,7 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L1012: isolated marker/symbol line :: 1</t>
+          <t>L997: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -6767,7 +6523,7 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L1014: symbol-only separator/garbage line :: 2, 90</t>
+          <t>L998: symbol-only separator/garbage line :: 1, 00</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -6798,7 +6554,7 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L1016: isolated marker/symbol line :: 4</t>
+          <t>L1002: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -6829,7 +6585,7 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L1020: symbol-only separator/garbage line :: 220.00</t>
+          <t>L1003: symbol-only separator/garbage line :: 5, 20</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -6860,7 +6616,7 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L1021: isolated marker/symbol line :: 1</t>
+          <t>L1007: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -6891,7 +6647,7 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L1025: symbol-only separator/garbage line :: 3.00</t>
+          <t>L1008: symbol-only separator/garbage line :: 20, 00</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -6922,7 +6678,7 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L1027: isolated marker/symbol line :: *</t>
+          <t>L1011: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -6953,7 +6709,7 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: ,</t>
+          <t>L1012: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -6984,7 +6740,7 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L1032: isolated marker/symbol line :: r</t>
+          <t>L1014: symbol-only separator/garbage line :: 2, 90</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7015,7 +6771,7 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: 0</t>
+          <t>L1016: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7046,7 +6802,7 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L1048: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L1020: symbol-only separator/garbage line :: 220.00</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr"/>
@@ -7077,7 +6833,7 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L1049: isolated marker/symbol line :: 1</t>
+          <t>L1021: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O166" s="1" t="inlineStr"/>
@@ -7108,7 +6864,7 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1025: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O167" s="1" t="inlineStr"/>
@@ -7139,7 +6895,7 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L1052: isolated marker/symbol line :: 0</t>
+          <t>L1027: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O168" s="1" t="inlineStr"/>
@@ -7170,7 +6926,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L1054: isolated marker/symbol line :: '</t>
+          <t>L1030: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -7201,7 +6957,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L1055: isolated marker/symbol line :: 000</t>
+          <t>L1032: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -7232,7 +6988,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L1056: symbol-only separator/garbage line :: 7.55</t>
+          <t>L1034: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -7263,7 +7019,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L1057: symbol-only separator/garbage line :: 50.00</t>
+          <t>L1036: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -7294,7 +7050,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L1058: isolated marker/symbol line :: :</t>
+          <t>L1048: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -7325,7 +7081,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L1059: symbol-only separator/garbage line :: 9, 16</t>
+          <t>L1049: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -7356,7 +7112,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L1060: isolated marker/symbol line :: 3</t>
+          <t>L1051: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -7387,7 +7143,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L1061: symbol-only separator/garbage line :: 24.00</t>
+          <t>L1052: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -7418,7 +7174,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L1062: isolated marker/symbol line :: ^</t>
+          <t>L1054: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -7433,6 +7189,285 @@
       <c r="X177" s="1" t="inlineStr"/>
       <c r="Y177" s="1" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr"/>
+      <c r="B178" s="1" t="inlineStr"/>
+      <c r="C178" s="1" t="inlineStr"/>
+      <c r="D178" s="1" t="inlineStr"/>
+      <c r="E178" s="1" t="inlineStr"/>
+      <c r="F178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr"/>
+      <c r="H178" s="1" t="inlineStr"/>
+      <c r="I178" s="1" t="inlineStr"/>
+      <c r="J178" s="1" t="inlineStr"/>
+      <c r="K178" s="1" t="inlineStr"/>
+      <c r="L178" s="1" t="inlineStr"/>
+      <c r="M178" s="1" t="inlineStr"/>
+      <c r="N178" s="1" t="inlineStr">
+        <is>
+          <t>L1055: isolated marker/symbol line :: 000</t>
+        </is>
+      </c>
+      <c r="O178" s="1" t="inlineStr"/>
+      <c r="P178" s="1" t="inlineStr"/>
+      <c r="Q178" s="1" t="inlineStr"/>
+      <c r="R178" s="1" t="inlineStr"/>
+      <c r="S178" s="1" t="inlineStr"/>
+      <c r="T178" s="1" t="inlineStr"/>
+      <c r="U178" s="1" t="inlineStr"/>
+      <c r="V178" s="1" t="inlineStr"/>
+      <c r="W178" s="1" t="inlineStr"/>
+      <c r="X178" s="1" t="inlineStr"/>
+      <c r="Y178" s="1" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr"/>
+      <c r="B179" s="1" t="inlineStr"/>
+      <c r="C179" s="1" t="inlineStr"/>
+      <c r="D179" s="1" t="inlineStr"/>
+      <c r="E179" s="1" t="inlineStr"/>
+      <c r="F179" s="1" t="inlineStr"/>
+      <c r="G179" s="1" t="inlineStr"/>
+      <c r="H179" s="1" t="inlineStr"/>
+      <c r="I179" s="1" t="inlineStr"/>
+      <c r="J179" s="1" t="inlineStr"/>
+      <c r="K179" s="1" t="inlineStr"/>
+      <c r="L179" s="1" t="inlineStr"/>
+      <c r="M179" s="1" t="inlineStr"/>
+      <c r="N179" s="1" t="inlineStr">
+        <is>
+          <t>L1056: symbol-only separator/garbage line :: 7.55</t>
+        </is>
+      </c>
+      <c r="O179" s="1" t="inlineStr"/>
+      <c r="P179" s="1" t="inlineStr"/>
+      <c r="Q179" s="1" t="inlineStr"/>
+      <c r="R179" s="1" t="inlineStr"/>
+      <c r="S179" s="1" t="inlineStr"/>
+      <c r="T179" s="1" t="inlineStr"/>
+      <c r="U179" s="1" t="inlineStr"/>
+      <c r="V179" s="1" t="inlineStr"/>
+      <c r="W179" s="1" t="inlineStr"/>
+      <c r="X179" s="1" t="inlineStr"/>
+      <c r="Y179" s="1" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr"/>
+      <c r="B180" s="1" t="inlineStr"/>
+      <c r="C180" s="1" t="inlineStr"/>
+      <c r="D180" s="1" t="inlineStr"/>
+      <c r="E180" s="1" t="inlineStr"/>
+      <c r="F180" s="1" t="inlineStr"/>
+      <c r="G180" s="1" t="inlineStr"/>
+      <c r="H180" s="1" t="inlineStr"/>
+      <c r="I180" s="1" t="inlineStr"/>
+      <c r="J180" s="1" t="inlineStr"/>
+      <c r="K180" s="1" t="inlineStr"/>
+      <c r="L180" s="1" t="inlineStr"/>
+      <c r="M180" s="1" t="inlineStr"/>
+      <c r="N180" s="1" t="inlineStr">
+        <is>
+          <t>L1057: symbol-only separator/garbage line :: 50.00</t>
+        </is>
+      </c>
+      <c r="O180" s="1" t="inlineStr"/>
+      <c r="P180" s="1" t="inlineStr"/>
+      <c r="Q180" s="1" t="inlineStr"/>
+      <c r="R180" s="1" t="inlineStr"/>
+      <c r="S180" s="1" t="inlineStr"/>
+      <c r="T180" s="1" t="inlineStr"/>
+      <c r="U180" s="1" t="inlineStr"/>
+      <c r="V180" s="1" t="inlineStr"/>
+      <c r="W180" s="1" t="inlineStr"/>
+      <c r="X180" s="1" t="inlineStr"/>
+      <c r="Y180" s="1" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr"/>
+      <c r="B181" s="1" t="inlineStr"/>
+      <c r="C181" s="1" t="inlineStr"/>
+      <c r="D181" s="1" t="inlineStr"/>
+      <c r="E181" s="1" t="inlineStr"/>
+      <c r="F181" s="1" t="inlineStr"/>
+      <c r="G181" s="1" t="inlineStr"/>
+      <c r="H181" s="1" t="inlineStr"/>
+      <c r="I181" s="1" t="inlineStr"/>
+      <c r="J181" s="1" t="inlineStr"/>
+      <c r="K181" s="1" t="inlineStr"/>
+      <c r="L181" s="1" t="inlineStr"/>
+      <c r="M181" s="1" t="inlineStr"/>
+      <c r="N181" s="1" t="inlineStr">
+        <is>
+          <t>L1058: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
+      <c r="O181" s="1" t="inlineStr"/>
+      <c r="P181" s="1" t="inlineStr"/>
+      <c r="Q181" s="1" t="inlineStr"/>
+      <c r="R181" s="1" t="inlineStr"/>
+      <c r="S181" s="1" t="inlineStr"/>
+      <c r="T181" s="1" t="inlineStr"/>
+      <c r="U181" s="1" t="inlineStr"/>
+      <c r="V181" s="1" t="inlineStr"/>
+      <c r="W181" s="1" t="inlineStr"/>
+      <c r="X181" s="1" t="inlineStr"/>
+      <c r="Y181" s="1" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr"/>
+      <c r="B182" s="1" t="inlineStr"/>
+      <c r="C182" s="1" t="inlineStr"/>
+      <c r="D182" s="1" t="inlineStr"/>
+      <c r="E182" s="1" t="inlineStr"/>
+      <c r="F182" s="1" t="inlineStr"/>
+      <c r="G182" s="1" t="inlineStr"/>
+      <c r="H182" s="1" t="inlineStr"/>
+      <c r="I182" s="1" t="inlineStr"/>
+      <c r="J182" s="1" t="inlineStr"/>
+      <c r="K182" s="1" t="inlineStr"/>
+      <c r="L182" s="1" t="inlineStr"/>
+      <c r="M182" s="1" t="inlineStr"/>
+      <c r="N182" s="1" t="inlineStr">
+        <is>
+          <t>L1059: symbol-only separator/garbage line :: 9, 16</t>
+        </is>
+      </c>
+      <c r="O182" s="1" t="inlineStr"/>
+      <c r="P182" s="1" t="inlineStr"/>
+      <c r="Q182" s="1" t="inlineStr"/>
+      <c r="R182" s="1" t="inlineStr"/>
+      <c r="S182" s="1" t="inlineStr"/>
+      <c r="T182" s="1" t="inlineStr"/>
+      <c r="U182" s="1" t="inlineStr"/>
+      <c r="V182" s="1" t="inlineStr"/>
+      <c r="W182" s="1" t="inlineStr"/>
+      <c r="X182" s="1" t="inlineStr"/>
+      <c r="Y182" s="1" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr"/>
+      <c r="B183" s="1" t="inlineStr"/>
+      <c r="C183" s="1" t="inlineStr"/>
+      <c r="D183" s="1" t="inlineStr"/>
+      <c r="E183" s="1" t="inlineStr"/>
+      <c r="F183" s="1" t="inlineStr"/>
+      <c r="G183" s="1" t="inlineStr"/>
+      <c r="H183" s="1" t="inlineStr"/>
+      <c r="I183" s="1" t="inlineStr"/>
+      <c r="J183" s="1" t="inlineStr"/>
+      <c r="K183" s="1" t="inlineStr"/>
+      <c r="L183" s="1" t="inlineStr"/>
+      <c r="M183" s="1" t="inlineStr"/>
+      <c r="N183" s="1" t="inlineStr">
+        <is>
+          <t>L1060: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O183" s="1" t="inlineStr"/>
+      <c r="P183" s="1" t="inlineStr"/>
+      <c r="Q183" s="1" t="inlineStr"/>
+      <c r="R183" s="1" t="inlineStr"/>
+      <c r="S183" s="1" t="inlineStr"/>
+      <c r="T183" s="1" t="inlineStr"/>
+      <c r="U183" s="1" t="inlineStr"/>
+      <c r="V183" s="1" t="inlineStr"/>
+      <c r="W183" s="1" t="inlineStr"/>
+      <c r="X183" s="1" t="inlineStr"/>
+      <c r="Y183" s="1" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr"/>
+      <c r="B184" s="1" t="inlineStr"/>
+      <c r="C184" s="1" t="inlineStr"/>
+      <c r="D184" s="1" t="inlineStr"/>
+      <c r="E184" s="1" t="inlineStr"/>
+      <c r="F184" s="1" t="inlineStr"/>
+      <c r="G184" s="1" t="inlineStr"/>
+      <c r="H184" s="1" t="inlineStr"/>
+      <c r="I184" s="1" t="inlineStr"/>
+      <c r="J184" s="1" t="inlineStr"/>
+      <c r="K184" s="1" t="inlineStr"/>
+      <c r="L184" s="1" t="inlineStr"/>
+      <c r="M184" s="1" t="inlineStr"/>
+      <c r="N184" s="1" t="inlineStr">
+        <is>
+          <t>L1061: symbol-only separator/garbage line :: 24.00</t>
+        </is>
+      </c>
+      <c r="O184" s="1" t="inlineStr"/>
+      <c r="P184" s="1" t="inlineStr"/>
+      <c r="Q184" s="1" t="inlineStr"/>
+      <c r="R184" s="1" t="inlineStr"/>
+      <c r="S184" s="1" t="inlineStr"/>
+      <c r="T184" s="1" t="inlineStr"/>
+      <c r="U184" s="1" t="inlineStr"/>
+      <c r="V184" s="1" t="inlineStr"/>
+      <c r="W184" s="1" t="inlineStr"/>
+      <c r="X184" s="1" t="inlineStr"/>
+      <c r="Y184" s="1" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr"/>
+      <c r="B185" s="1" t="inlineStr"/>
+      <c r="C185" s="1" t="inlineStr"/>
+      <c r="D185" s="1" t="inlineStr"/>
+      <c r="E185" s="1" t="inlineStr"/>
+      <c r="F185" s="1" t="inlineStr"/>
+      <c r="G185" s="1" t="inlineStr"/>
+      <c r="H185" s="1" t="inlineStr"/>
+      <c r="I185" s="1" t="inlineStr"/>
+      <c r="J185" s="1" t="inlineStr"/>
+      <c r="K185" s="1" t="inlineStr"/>
+      <c r="L185" s="1" t="inlineStr"/>
+      <c r="M185" s="1" t="inlineStr"/>
+      <c r="N185" s="1" t="inlineStr">
+        <is>
+          <t>L1062: isolated marker/symbol line :: ^</t>
+        </is>
+      </c>
+      <c r="O185" s="1" t="inlineStr"/>
+      <c r="P185" s="1" t="inlineStr"/>
+      <c r="Q185" s="1" t="inlineStr"/>
+      <c r="R185" s="1" t="inlineStr"/>
+      <c r="S185" s="1" t="inlineStr"/>
+      <c r="T185" s="1" t="inlineStr"/>
+      <c r="U185" s="1" t="inlineStr"/>
+      <c r="V185" s="1" t="inlineStr"/>
+      <c r="W185" s="1" t="inlineStr"/>
+      <c r="X185" s="1" t="inlineStr"/>
+      <c r="Y185" s="1" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr"/>
+      <c r="B186" s="1" t="inlineStr"/>
+      <c r="C186" s="1" t="inlineStr"/>
+      <c r="D186" s="1" t="inlineStr"/>
+      <c r="E186" s="1" t="inlineStr"/>
+      <c r="F186" s="1" t="inlineStr"/>
+      <c r="G186" s="1" t="inlineStr"/>
+      <c r="H186" s="1" t="inlineStr"/>
+      <c r="I186" s="1" t="inlineStr"/>
+      <c r="J186" s="1" t="inlineStr"/>
+      <c r="K186" s="1" t="inlineStr"/>
+      <c r="L186" s="1" t="inlineStr"/>
+      <c r="M186" s="1" t="inlineStr"/>
+      <c r="N186" s="1" t="inlineStr">
+        <is>
+          <t>L1063: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O186" s="1" t="inlineStr"/>
+      <c r="P186" s="1" t="inlineStr"/>
+      <c r="Q186" s="1" t="inlineStr"/>
+      <c r="R186" s="1" t="inlineStr"/>
+      <c r="S186" s="1" t="inlineStr"/>
+      <c r="T186" s="1" t="inlineStr"/>
+      <c r="U186" s="1" t="inlineStr"/>
+      <c r="V186" s="1" t="inlineStr"/>
+      <c r="W186" s="1" t="inlineStr"/>
+      <c r="X186" s="1" t="inlineStr"/>
+      <c r="Y186" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
